--- a/fix-errors/ig/FRSectionExaminationReportLMCDAFHIR.xlsx
+++ b/fix-errors/ig/FRSectionExaminationReportLMCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T08:13:43+00:00</t>
+    <t>2026-08-18T11:25:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -103,13 +103,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-examination-report</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-examination-report|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-dicom-acte-imagerie</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-dicom-acte-imagerie|0.1.0</t>
   </si>
   <si>
     <t>FRLMExaminationReport</t>
@@ -151,7 +151,7 @@
     <t>FRCDADICOMActeImagerie.entry.frDICOMAdministrationProduitDeSante</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-dicom-conclusion</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-dicom-conclusion|0.1.0</t>
   </si>
   <si>
     <t>FRLMExaminationReport.subSection.conclusion</t>
@@ -160,7 +160,7 @@
     <t>FRCDASectionDICOMConclusion</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-dicom-resultats</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-dicom-resultats|0.1.0</t>
   </si>
   <si>
     <t>FRLMExaminationReport.entry.results[x]</t>
@@ -169,7 +169,7 @@
     <t>FRCDADICOMResultats</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-composition-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-composition-document|0.1.0</t>
   </si>
   <si>
     <t>FRCompositionDocument.section:sectionImpression</t>
@@ -193,7 +193,7 @@
     <t>FRCompositionDocument.section:Findings.entry:FRObservationResultDocument</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-diagnostic-report-imaging-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-diagnostic-report-imaging-document|0.1.0</t>
   </si>
   <si>
     <t>FRDiagnosticReportImagingDocument.conclusion</t>
